--- a/output/details/2026-05-07/preprocessed_data.xlsx
+++ b/output/details/2026-05-07/preprocessed_data.xlsx
@@ -15231,25 +15231,25 @@
         <v>46149</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.1079781178463906</v>
+        <v>-0.1075103561022022</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2041149961916046</v>
+        <v>-0.132193159953179</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2038196090885085</v>
+        <v>-0.1319301230822154</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1339405138202139</v>
+        <v>0.01600334164150592</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001703785565784616</v>
+        <v>0.001704151380668061</v>
       </c>
       <c r="G2" t="n">
-        <v>1.771032515408005</v>
+        <v>2.354592014437191</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4634137938913881</v>
+        <v>-0.2565322379880431</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
